--- a/artfynd/A 58034-2022 artfynd.xlsx
+++ b/artfynd/A 58034-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58034-2022 artfynd.xlsx
+++ b/artfynd/A 58034-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114687636</v>
+        <v>114687633</v>
       </c>
       <c r="B2" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>862116</v>
+        <v>862075</v>
       </c>
       <c r="R2" t="n">
-        <v>7494921</v>
+        <v>7494909</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-09-14</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gammalt träd</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,37 +778,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114687655</v>
+        <v>114687635</v>
       </c>
       <c r="B3" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -818,10 +813,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>862296</v>
+        <v>862075</v>
       </c>
       <c r="R3" t="n">
-        <v>7494767</v>
+        <v>7494895</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,37 +876,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114687643</v>
+        <v>114687636</v>
       </c>
       <c r="B4" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2166</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -921,10 +911,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>862193</v>
+        <v>862116</v>
       </c>
       <c r="R4" t="n">
-        <v>7494871</v>
+        <v>7494921</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114687637</v>
+        <v>114687642</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1000,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>862135</v>
+        <v>862195</v>
       </c>
       <c r="R5" t="n">
-        <v>7494928</v>
+        <v>7494869</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,37 +1072,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114687633</v>
+        <v>114687639</v>
       </c>
       <c r="B6" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>2166</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1107,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>862075</v>
+        <v>862188</v>
       </c>
       <c r="R6" t="n">
-        <v>7494909</v>
+        <v>7494899</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,11 +1143,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gammalt träd</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,37 +1170,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114687632</v>
+        <v>114687643</v>
       </c>
       <c r="B7" t="n">
-        <v>77895</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>2166</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>862086</v>
+        <v>862193</v>
       </c>
       <c r="R7" t="n">
-        <v>7494926</v>
+        <v>7494871</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1298,15 +1268,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114687639</v>
+        <v>114687654</v>
       </c>
       <c r="B8" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>862188</v>
+        <v>862287</v>
       </c>
       <c r="R8" t="n">
-        <v>7494899</v>
+        <v>7494767</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1401,15 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114687654</v>
+        <v>114687655</v>
       </c>
       <c r="B9" t="n">
-        <v>94324</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,7 +1401,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>862287</v>
+        <v>862296</v>
       </c>
       <c r="R9" t="n">
         <v>7494767</v>
@@ -1504,15 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>114687641</v>
+        <v>114687632</v>
       </c>
       <c r="B10" t="n">
-        <v>74647</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1520,21 +1475,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>862201</v>
+        <v>862086</v>
       </c>
       <c r="R10" t="n">
-        <v>7494871</v>
+        <v>7494926</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,15 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>114687642</v>
+        <v>114687641</v>
       </c>
       <c r="B11" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1623,21 +1573,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1597,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>862195</v>
+        <v>862201</v>
       </c>
       <c r="R11" t="n">
-        <v>7494869</v>
+        <v>7494871</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1707,109 +1657,6 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114687635</v>
-      </c>
-      <c r="B12" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>1312</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Gammelgransskål</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Pseudographis pinicola</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Riukanjärvi, Nb</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>862075</v>
-      </c>
-      <c r="R12" t="n">
-        <v>7494895</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Pajala</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58034-2022 artfynd.xlsx
+++ b/artfynd/A 58034-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1658,6 +1658,818 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>134752667</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57125</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>862258</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7494848</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>06:27</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>134752665</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>862163</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7495228</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134752666</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57386</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>102954</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Gallinago gallinago</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>862204</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7494868</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>134752650</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>862148</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7495263</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>07:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134752656</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>862177</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7494912</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>07:04</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134752655</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>862002</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7495280</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134752668</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58596</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kaunisvaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>862306</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7494791</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-05-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>06:19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 58034-2022 artfynd.xlsx
+++ b/artfynd/A 58034-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -775,6 +780,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687633</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -873,6 +883,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687635</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687636</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1069,6 +1089,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687642</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1167,6 +1192,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687639</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1265,6 +1295,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687643</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687654</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687655</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687632</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1657,6 +1707,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114687641</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1773,6 +1828,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752667</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752666</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2005,6 +2070,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752656</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2121,6 +2191,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752668</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2237,6 +2312,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752665</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2353,6 +2433,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752650</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2469,8 +2554,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134752655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>